--- a/www/download/IND.compensation.empe_ls.r.pc.WIOD13.xlsx
+++ b/www/download/IND.compensation.empe_ls.r.pc.WIOD13.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>43.91</t>
+          <t>0.439089920935031</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>43.23</t>
+          <t>0.43232496849829</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>42.51</t>
+          <t>0.425147874602951</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>41.75</t>
+          <t>0.41754189002325</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>0.409484448138053</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>40.09</t>
+          <t>0.400947169999198</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>39.19</t>
+          <t>0.391895596574286</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>38.53</t>
+          <t>0.385326224316197</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>38.03</t>
+          <t>0.380315087083958</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>36.92</t>
+          <t>0.369233821286366</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>35.79</t>
+          <t>0.357913324699458</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>35.79</t>
+          <t>0.357913324699458</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>35.79</t>
+          <t>0.357913324699458</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>35.79</t>
+          <t>0.357913324699458</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>35.79</t>
+          <t>0.357913324699458</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>15.99</t>
+          <t>0.159945016625794</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>15.09</t>
+          <t>0.150858627033873</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>14.59</t>
+          <t>0.145896192681503</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>14.68</t>
+          <t>0.146819937643385</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>14.35</t>
+          <t>0.143526374487177</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>0.142044981307112</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>13.54</t>
+          <t>0.135351420942655</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>13.15</t>
+          <t>0.131519931137443</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>16.83</t>
+          <t>0.168304933330319</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>11.94</t>
+          <t>0.1194340007528</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>11.65</t>
+          <t>0.11651511569277</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>12.17</t>
+          <t>0.121664774535988</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>12.03</t>
+          <t>0.120250721437629</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>11.05</t>
+          <t>0.110486946016944</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>10.05</t>
+          <t>0.100508168515127</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>38.86</t>
+          <t>0.388630537896201</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>37.24</t>
+          <t>0.372408518302289</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>35.97</t>
+          <t>0.359727994089643</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>34.9</t>
+          <t>0.349037801058688</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>0.342390568495337</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>32.18</t>
+          <t>0.321806099352027</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>30.88</t>
+          <t>0.308786327802769</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>30.02</t>
+          <t>0.30022810052614</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>33.09</t>
+          <t>0.330913494461304</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>26.31</t>
+          <t>0.263084342524089</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>25.01</t>
+          <t>0.250119214235193</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>24.04</t>
+          <t>0.240389067932242</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>22.29</t>
+          <t>0.222872556115051</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>21.15</t>
+          <t>0.21148502721606</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>20.54</t>
+          <t>0.20540004415022</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>67.69</t>
+          <t>0.676942541134211</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>67.16</t>
+          <t>0.671583467240692</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>68.99</t>
+          <t>0.689949695486209</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>70.87</t>
+          <t>0.708697315321728</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>69.03</t>
+          <t>0.690295663773374</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>68.25</t>
+          <t>0.682461242673443</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>67.83</t>
+          <t>0.678322809878038</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>0.675013197647998</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>0.742957640479934</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>63.28</t>
+          <t>0.632826782898329</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>62.12</t>
+          <t>0.621231098949445</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>60.76</t>
+          <t>0.607593264151529</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>60.99</t>
+          <t>0.609852186050824</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>59.46</t>
+          <t>0.594598354172337</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>57.12</t>
+          <t>0.57123482977503</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>38.33</t>
+          <t>0.383309045496929</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>37.43</t>
+          <t>0.374284183424795</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>36.53</t>
+          <t>0.365259321352662</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>35.62</t>
+          <t>0.356234459280528</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>34.72</t>
+          <t>0.347209597208395</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>33.82</t>
+          <t>0.338184735136261</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>32.92</t>
+          <t>0.329159873064128</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>32.01</t>
+          <t>0.320135010991994</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>31.07</t>
+          <t>0.310699257445443</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>30.13</t>
+          <t>0.301263503898892</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>29.18</t>
+          <t>0.291827750352342</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>28.14</t>
+          <t>0.28135348760452</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>27.09</t>
+          <t>0.270879224856699</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>26.04</t>
+          <t>0.260404962108878</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>0.249930699361057</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>0.0573929821675975</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>0.0528816592979775</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>0.0502988998164565</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>0.0481847893652541</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>0.0428835575080581</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>0.0399444874783705</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>0.0376635887154743</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>0.0375116248191324</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>0.0353158250441179</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>0.0335442894785202</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>0.03128770542763</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>0.0302303754872812</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>0.0267088480864822</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>0.0265027844380628</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>0.0256935423471342</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>44.29</t>
+          <t>0.442857123957802</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>43.06</t>
+          <t>0.430587825971414</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>41.84</t>
+          <t>0.418379011603576</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>40.62</t>
+          <t>0.406244794312433</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>39.42</t>
+          <t>0.394198969761176</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>38.23</t>
+          <t>0.382254962087824</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>37.04</t>
+          <t>0.370425772753534</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>35.87</t>
+          <t>0.35872393269315</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>0.360406728417528</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>0.368011539833063</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>36.49</t>
+          <t>0.364918511085427</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>36.27</t>
+          <t>0.362742024616758</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>0.371022163542786</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>36.62</t>
+          <t>0.36624317771296</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>36.62</t>
+          <t>0.36624317771296</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>28.86</t>
+          <t>0.288589871356368</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>0.286468694434018</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>0.307680339890158</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>33.19</t>
+          <t>0.331876236690805</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>30.94</t>
+          <t>0.30936848043065</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>29.87</t>
+          <t>0.298739921775052</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>0.296495476649359</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>29.28</t>
+          <t>0.292826023543989</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>32.19</t>
+          <t>0.321859735941472</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>26.96</t>
+          <t>0.269564557292643</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>27.32</t>
+          <t>0.273205511385408</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>25.89</t>
+          <t>0.258880782769327</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>0.247159243432374</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>0.242949470218427</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>23.83</t>
+          <t>0.238269081935171</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>0.0666657828285725</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>0.0666657828285725</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>0.0666657828285725</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>0.0666657828285725</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>0.0657009348582706</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6.42</t>
+          <t>0.0642072145308483</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5.96</t>
+          <t>0.0596129501008513</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>0.0582845073737414</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>7.99</t>
+          <t>0.0798654275051914</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>0.0502042285923985</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>0.0460672435298555</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>4.62</t>
+          <t>0.0461586131512284</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>0.0497960840766058</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>4.99</t>
+          <t>0.0498643995243779</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>0.0457581862959489</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>11.31</t>
+          <t>0.113098406687083</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>11.03</t>
+          <t>0.110295293251868</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>10.88</t>
+          <t>0.108844378009404</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>10.61</t>
+          <t>0.106104707020097</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>11.09</t>
+          <t>0.110918826437064</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>0.113487060109063</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>0.114198365190309</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>11.21</t>
+          <t>0.112079629754133</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>11.19</t>
+          <t>0.111900786831642</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>0.0988852049797545</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>0.110407023753181</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>10.84</t>
+          <t>0.108435741094531</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>10.47</t>
+          <t>0.104719014311994</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>0.0973098363683425</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>0.0924362159780996</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>0.225525809543505</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>21.64</t>
+          <t>0.216404227627882</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>0.209966204373871</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>20.09</t>
+          <t>0.200864841656351</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>19.43</t>
+          <t>0.19426348428818</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>0.18954898568834</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>18.28</t>
+          <t>0.182788258925276</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>17.84</t>
+          <t>0.178363286953914</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>17.94</t>
+          <t>0.179422447482985</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>18.03</t>
+          <t>0.180315441839504</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>18.89</t>
+          <t>0.188884080028084</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>0.179473494878193</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>0.243537037687662</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>22.28</t>
+          <t>0.222837296724283</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>23.63</t>
+          <t>0.236308212315941</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>56.48</t>
+          <t>0.564822567954968</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>53.52</t>
+          <t>0.535225899384799</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>52.07</t>
+          <t>0.520683709272383</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>49.72</t>
+          <t>0.497241324500948</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>48.35</t>
+          <t>0.483507210684685</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>45.94</t>
+          <t>0.459408810412681</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>44.77</t>
+          <t>0.447732415544772</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>43.62</t>
+          <t>0.436219852474868</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>47.71</t>
+          <t>0.477082351900684</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>41.11</t>
+          <t>0.411066544264968</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>38.39</t>
+          <t>0.383903765589567</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>37.38</t>
+          <t>0.37383662181419</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>37.28</t>
+          <t>0.372799409265536</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>36.97</t>
+          <t>0.369698591731777</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>35.92</t>
+          <t>0.359156445617952</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>0.0712091295758107</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>7.04</t>
+          <t>0.0703735977329677</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>7.82</t>
+          <t>0.0781873830584773</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>8.79</t>
+          <t>0.0878511306498983</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>7.78</t>
+          <t>0.0778351044296063</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>0.0741376189329238</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>7.35</t>
+          <t>0.0734894151736126</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>0.072020018608464</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>10.89</t>
+          <t>0.108934697260279</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>7.85</t>
+          <t>0.0785401450228414</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>0.0720330222924337</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>8.43</t>
+          <t>0.0843182593720788</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>8.66</t>
+          <t>0.0865893748544551</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>9.93</t>
+          <t>0.0992576432356307</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>0.0867087070013527</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>27.85</t>
+          <t>0.278485049268878</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>0.26604791163542</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>25.62</t>
+          <t>0.256163173235223</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>0.246537208456252</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>0.234591167609826</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>22.63</t>
+          <t>0.2262717375792</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>21.94</t>
+          <t>0.219384958269592</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>0.210960141947581</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>21.89</t>
+          <t>0.218890539019971</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>18.67</t>
+          <t>0.186673029061948</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>0.183491461249212</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>17.66</t>
+          <t>0.176641201601009</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>17.34</t>
+          <t>0.173393947687707</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>16.99</t>
+          <t>0.169852350403836</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>15.68</t>
+          <t>0.156802800307778</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>31.32</t>
+          <t>0.313247564628499</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>30.36</t>
+          <t>0.30362294740479</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>29.91</t>
+          <t>0.299062386133083</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>28.76</t>
+          <t>0.287563707092355</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>27.53</t>
+          <t>0.275342026862405</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>26.57</t>
+          <t>0.265733950234225</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>25.85</t>
+          <t>0.258503440489157</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>25.09</t>
+          <t>0.250901575069065</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>0.294955366130374</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>24.18</t>
+          <t>0.2417801820928</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>0.232457479600205</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>0.229958637551458</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>0.216049080556083</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>0.206466899166584</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>0.20132401226695</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>30.69</t>
+          <t>0.30692945395714</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>29.89</t>
+          <t>0.298881622964842</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>26.54</t>
+          <t>0.265356738263519</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>24.98</t>
+          <t>0.249831402138882</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>23.88</t>
+          <t>0.238843383382723</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>23.23</t>
+          <t>0.232341286466559</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>23.77</t>
+          <t>0.23767633035999</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>22.57</t>
+          <t>0.225651833854026</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>0.206500573077058</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>19.72</t>
+          <t>0.197176443552562</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>19.33</t>
+          <t>0.193290947882933</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>0.185047998689349</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>18.81</t>
+          <t>0.188091354739622</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>18.34</t>
+          <t>0.183394237037994</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>0.17400225663909</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>48.37</t>
+          <t>0.483687474553789</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>46.09</t>
+          <t>0.460864092842412</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>43.45</t>
+          <t>0.434495559420457</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>40.72</t>
+          <t>0.407171086515346</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>38.06</t>
+          <t>0.380647012426368</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>35.92</t>
+          <t>0.359195215030561</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>36.36</t>
+          <t>0.363627057603692</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>34.35</t>
+          <t>0.343511825445232</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>37.19</t>
+          <t>0.371855821813671</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>0.30602928367531</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>30.49</t>
+          <t>0.304902060918577</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>33.76</t>
+          <t>0.337619926763533</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>33.05</t>
+          <t>0.330453289710311</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>32.67</t>
+          <t>0.326673407126065</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>32.97</t>
+          <t>0.329657664925441</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>13.74</t>
+          <t>0.13743399879016</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>13.74</t>
+          <t>0.13743399879016</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>13.74</t>
+          <t>0.13743399879016</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>13.74</t>
+          <t>0.13743399879016</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>10.97</t>
+          <t>0.109680649152924</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>12.91</t>
+          <t>0.129052369162755</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>12.79</t>
+          <t>0.127933185268661</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>12.38</t>
+          <t>0.123772921231317</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>18.53</t>
+          <t>0.185311532802071</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>10.94</t>
+          <t>0.109410941777007</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>10.69</t>
+          <t>0.106858359831521</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>0.0988851081286282</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>9.86</t>
+          <t>0.0985929649736658</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>0.0929972084387651</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>0.08350337139528</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>51.33</t>
+          <t>0.513297574690318</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>51.33</t>
+          <t>0.513297574690318</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>50.29</t>
+          <t>0.502907302913139</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>49.54</t>
+          <t>0.49538590126897</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>50.89</t>
+          <t>0.508863829601591</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>46.48</t>
+          <t>0.464758440147982</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>47.09</t>
+          <t>0.47086385496248</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>45.99</t>
+          <t>0.459899440441751</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>45.44</t>
+          <t>0.454417233181387</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>44.89</t>
+          <t>0.448935025921022</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>43.65</t>
+          <t>0.436482098049651</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>43.03</t>
+          <t>0.430255634113966</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>0.419042665439079</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>0.419042665439079</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>0.419042665439079</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>35.8</t>
+          <t>0.357977236698742</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>34.98</t>
+          <t>0.349755411504265</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>34.15</t>
+          <t>0.341533586309788</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.333311761115311</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>32.51</t>
+          <t>0.325089935920834</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>32.02</t>
+          <t>0.320236235786034</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>31.54</t>
+          <t>0.315382535651234</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>31.05</t>
+          <t>0.310528835516434</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>30.57</t>
+          <t>0.305675135381635</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>30.08</t>
+          <t>0.300821435246835</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>30.08</t>
+          <t>0.300821435246835</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>30.08</t>
+          <t>0.300821435246835</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>30.08</t>
+          <t>0.300821435246835</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>30.08</t>
+          <t>0.300821435246835</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>30.08</t>
+          <t>0.300821435246835</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>0.350460372283722</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>31.85</t>
+          <t>0.318517885751064</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>30.02</t>
+          <t>0.300207707341319</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>0.287269121702744</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>0.276526565321358</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>0.272668942156071</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>27.3</t>
+          <t>0.273023934964769</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>25.97</t>
+          <t>0.259694347150962</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>24.74</t>
+          <t>0.247362106257369</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>24.33</t>
+          <t>0.243272926676302</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>24.76</t>
+          <t>0.247557810935509</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>21.19</t>
+          <t>0.211933392649964</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>0.219638289381567</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>21.28</t>
+          <t>0.212847377498389</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>18.87</t>
+          <t>0.188677067027303</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>55.46</t>
+          <t>0.554588407815023</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>52.77</t>
+          <t>0.527721549626007</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>49.97</t>
+          <t>0.499745568913894</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>0.470563199247354</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>45.19</t>
+          <t>0.451927984954686</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>42.3</t>
+          <t>0.423022153670912</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>44.04</t>
+          <t>0.44042157677094</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>42.93</t>
+          <t>0.429287677806325</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>46.68</t>
+          <t>0.466768200886961</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>39.47</t>
+          <t>0.39471835773429</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>38.12</t>
+          <t>0.3812414111076</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>36.77</t>
+          <t>0.367730556595476</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>36.38</t>
+          <t>0.363763011321344</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>36.08</t>
+          <t>0.360830620506057</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>35.45</t>
+          <t>0.354546063306387</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>15.81</t>
+          <t>0.158140003356385</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>0.147030896598676</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>0.139973846650393</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>12.81</t>
+          <t>0.128099919740821</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>11.97</t>
+          <t>0.119706968470586</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>11.25</t>
+          <t>0.112478836637586</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>0.10165777433117</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>0.0941558904206893</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>0.0859676869298493</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>0.0839298807997789</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>8.34</t>
+          <t>0.0834428540695712</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>8.34</t>
+          <t>0.0834428540695712</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>8.34</t>
+          <t>0.0834428540695712</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>8.34</t>
+          <t>0.0834428540695712</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>8.34</t>
+          <t>0.0834428540695712</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>0.203544937111852</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>18.69</t>
+          <t>0.186941831018976</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>17.58</t>
+          <t>0.175791620163351</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>15.67</t>
+          <t>0.156716680514124</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>15.46</t>
+          <t>0.15458125513764</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>14.39</t>
+          <t>0.143873997758355</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>0.125686562528887</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>10.99</t>
+          <t>0.109872871637817</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>10.46</t>
+          <t>0.10458479151308</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>0.0920090532044868</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>8.62</t>
+          <t>0.0861606581312238</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>8.62</t>
+          <t>0.0861606581312238</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>8.62</t>
+          <t>0.0861606581312238</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>8.62</t>
+          <t>0.0861606581312238</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>8.62</t>
+          <t>0.0861606581312238</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>6.59</t>
+          <t>0.0658595515676768</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>6.49</t>
+          <t>0.0649271987437972</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>7.19</t>
+          <t>0.0718974145860885</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>0.0804716745094041</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>7.19</t>
+          <t>0.0719082389027571</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>0.0690491330702188</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>0.0685058271409187</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>0.0662944207428411</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>7.82</t>
+          <t>0.0781525821328311</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>0.0623078256882247</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>5.79</t>
+          <t>0.0579390127043173</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>5.55</t>
+          <t>0.0555073566859132</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>0.0710278273595789</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>6.42</t>
+          <t>0.0641569347125852</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>0.0656136945520701</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>45.62</t>
+          <t>0.456215757513712</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>45.95</t>
+          <t>0.459521806594679</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>41.66</t>
+          <t>0.416564390471611</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>35.85</t>
+          <t>0.358488001139748</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>30.51</t>
+          <t>0.305093068109356</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>29.74</t>
+          <t>0.297425588481156</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>30.37</t>
+          <t>0.303734770314071</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>30.54</t>
+          <t>0.305398003950004</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>42.06</t>
+          <t>0.420560045752916</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>28.02</t>
+          <t>0.280222396549656</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>26.94</t>
+          <t>0.269426671118657</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>28.3</t>
+          <t>0.282993734964772</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>28.01</t>
+          <t>0.280095250948624</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>27.91</t>
+          <t>0.279123235576134</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>20.16</t>
+          <t>0.201585583395466</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>0.110211623596336</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>10.91</t>
+          <t>0.109136473959937</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>11.97</t>
+          <t>0.119707513241975</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>13.24</t>
+          <t>0.13239503907628</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>11.83</t>
+          <t>0.118343353660248</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>11.41</t>
+          <t>0.114115368725373</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>11.33</t>
+          <t>0.113345507380347</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>11.06</t>
+          <t>0.110609673388401</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>14.32</t>
+          <t>0.143166425640996</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>9.79</t>
+          <t>0.0979382469456849</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>10.86</t>
+          <t>0.108635907281014</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>10.64</t>
+          <t>0.106412652134116</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>11.23</t>
+          <t>0.112260643058987</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>10.32</t>
+          <t>0.103174017174459</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>0.0933107681148805</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>23.4</t>
+          <t>0.233976956708023</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>0.231032209132613</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>0.220028403453091</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>21.57</t>
+          <t>0.215736987253359</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>21.63</t>
+          <t>0.216341896244131</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>21.72</t>
+          <t>0.217156034167441</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>20.58</t>
+          <t>0.205803729187298</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>20.31</t>
+          <t>0.203076265115992</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>0.196982560963796</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>18.83</t>
+          <t>0.188282873967219</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>18.53</t>
+          <t>0.185260849308986</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>17.72</t>
+          <t>0.177171412655655</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>17.58</t>
+          <t>0.175811480877015</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>0.171959642619547</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>0.171959642619547</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>67.69</t>
+          <t>0.676942541134211</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>67.16</t>
+          <t>0.671583467240692</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>68.99</t>
+          <t>0.689949695486209</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>70.87</t>
+          <t>0.708697315321728</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>69.03</t>
+          <t>0.690295663773374</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>68.25</t>
+          <t>0.682461242673443</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>67.83</t>
+          <t>0.678322809878038</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>0.675013197647998</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>0.742957640479934</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>63.28</t>
+          <t>0.632826782898329</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>62.12</t>
+          <t>0.621231098949445</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>60.76</t>
+          <t>0.607593264151529</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>60.99</t>
+          <t>0.609852186050824</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>59.46</t>
+          <t>0.594598354172337</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>57.12</t>
+          <t>0.57123482977503</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>32.43</t>
+          <t>0.324268970037095</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>30.57</t>
+          <t>0.305747405310566</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>0.287983831174471</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>29.33</t>
+          <t>0.293250579780998</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>26.88</t>
+          <t>0.268847842775994</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>30.27</t>
+          <t>0.302675431457219</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>30.58</t>
+          <t>0.305777192543793</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>27.36</t>
+          <t>0.273557267169439</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>30.57</t>
+          <t>0.30571974785769</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>0.243156267283421</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>23.72</t>
+          <t>0.237194988014493</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>23.89</t>
+          <t>0.238949098288464</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>23.98</t>
+          <t>0.239779244084168</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>24.86</t>
+          <t>0.24860070855167</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>0.245536957434543</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>0.0735927596021157</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>0.0735927596021157</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>0.0735927596021157</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>0.0735927596021157</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>0.0735927596021157</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>0.0735927596021157</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>7.19</t>
+          <t>0.0718701324282859</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>0.0650589497872431</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>8.52</t>
+          <t>0.0851943629297249</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>5.23</t>
+          <t>0.0523050174793255</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>0.0494371527635151</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>0.0484763726921036</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>0.0484550183608254</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>5.16</t>
+          <t>0.0515561069851239</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>0.0493289443262993</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>67.69</t>
+          <t>0.676942541134211</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>67.16</t>
+          <t>0.671583467240692</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>68.99</t>
+          <t>0.689949695486209</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>70.87</t>
+          <t>0.708697315321728</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>69.03</t>
+          <t>0.690295663773374</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>68.25</t>
+          <t>0.682461242673443</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>67.83</t>
+          <t>0.678322809878038</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>0.675013197647998</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>0.742957640479934</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>63.28</t>
+          <t>0.632826782898329</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>62.12</t>
+          <t>0.621231098949445</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>60.76</t>
+          <t>0.607593264151529</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>60.99</t>
+          <t>0.609852186050824</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>59.46</t>
+          <t>0.594598354172337</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>57.12</t>
+          <t>0.57123482977503</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>67.69</t>
+          <t>0.676942541134211</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>67.16</t>
+          <t>0.671583467240692</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>68.99</t>
+          <t>0.689949695486209</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>70.87</t>
+          <t>0.708697315321728</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>69.03</t>
+          <t>0.690295663773374</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>68.25</t>
+          <t>0.682461242673443</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>67.83</t>
+          <t>0.678322809878038</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>0.675013197647998</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>0.742957640479934</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>63.28</t>
+          <t>0.632826782898329</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>62.12</t>
+          <t>0.621231098949445</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>60.76</t>
+          <t>0.607593264151529</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>60.99</t>
+          <t>0.609852186050824</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>59.46</t>
+          <t>0.594598354172337</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>57.12</t>
+          <t>0.57123482977503</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>0.0651088048616247</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>0.0651088048616247</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>0.0651088048616247</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>0.0651088048616247</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>6.42</t>
+          <t>0.0641997400185345</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>6.29</t>
+          <t>0.0628734273036245</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>0.0583218483621743</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>0.056988735556694</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>5.23</t>
+          <t>0.0522999523392593</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>4.78</t>
+          <t>0.0477809250524804</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>0.0452754712869191</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>0.0452754712869191</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>0.0452754712869191</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>0.0452754712869191</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>0.0452754712869191</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>6.97</t>
+          <t>0.0697202554724135</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>6.97</t>
+          <t>0.0697202554724135</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>6.97</t>
+          <t>0.0697202554724135</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>6.97</t>
+          <t>0.0697202554724135</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>0.0577799619984186</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>0.0498063483420509</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>0.0465072803986258</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>0.041313115045446</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>0.0632714556452081</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>0.0368069037205545</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>0.0331720382760451</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>0.0319790656741731</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>0.0321604506331831</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>0.0401377093857823</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>0.03634996541285</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>12.87</t>
+          <t>0.128698442586853</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>12.87</t>
+          <t>0.128698442586853</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>12.87</t>
+          <t>0.128698442586853</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>12.87</t>
+          <t>0.128698442586853</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>11.43</t>
+          <t>0.114339926549217</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>11.72</t>
+          <t>0.117170926244746</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>0.130999487813169</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>12.17</t>
+          <t>0.121726692529977</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>11.38</t>
+          <t>0.113835205782666</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>10.54</t>
+          <t>0.105441435142982</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>10.05</t>
+          <t>0.100538847843732</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>0.0949996209304649</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>10.14</t>
+          <t>0.101374501487387</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>9.83</t>
+          <t>0.0983375438427051</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>0.0913883061955541</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>25.61</t>
+          <t>0.256104045314381</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>24.68</t>
+          <t>0.24680560110718</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>23.72</t>
+          <t>0.23721826733424</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>0.228518568367287</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>22.61</t>
+          <t>0.226066781753345</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>0.198991968052896</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>19.13</t>
+          <t>0.19127195326067</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>18.49</t>
+          <t>0.184862481749466</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>19.58</t>
+          <t>0.195807220756769</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>17.66</t>
+          <t>0.176647183385259</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>16.97</t>
+          <t>0.16967946095763</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>0.165991083987865</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>0.167044287979174</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>0.159021295989738</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>17.69</t>
+          <t>0.176946882095448</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>57.93</t>
+          <t>0.579278627675349</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>56.09</t>
+          <t>0.560934466729406</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>54.43</t>
+          <t>0.544278558119174</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>54.19</t>
+          <t>0.54188926868477</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>52.87</t>
+          <t>0.52867461337197</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>51.43</t>
+          <t>0.51425352197</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>49.87</t>
+          <t>0.498676227594436</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>48.36</t>
+          <t>0.483609737815248</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>46.23</t>
+          <t>0.462343269883162</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>0.479040518672372</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>46.43</t>
+          <t>0.464319983436165</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>45.43</t>
+          <t>0.454269744389243</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>43.98</t>
+          <t>0.439766222489029</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>43.08</t>
+          <t>0.430812498357921</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>42.21</t>
+          <t>0.422122501623098</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>0.412995120935543</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>0.401339397161003</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>38.98</t>
+          <t>0.389848766606239</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>37.85</t>
+          <t>0.378519242977886</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>36.73</t>
+          <t>0.367347044103081</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>35.63</t>
+          <t>0.356328577952332</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>34.55</t>
+          <t>0.345460429984641</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>33.47</t>
+          <t>0.334739351669787</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>32.72</t>
+          <t>0.327154710375368</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>31.96</t>
+          <t>0.319642800111757</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>31.62</t>
+          <t>0.316204986394807</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>0.304531537626061</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>30.38</t>
+          <t>0.303763349529303</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>29.38</t>
+          <t>0.293754624826032</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>25.48</t>
+          <t>0.254815226876912</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>9.94</t>
+          <t>0.0994158199142756</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>0.0946098757751858</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>0.103020477389742</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>9.21</t>
+          <t>0.0921431323304222</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>9.17</t>
+          <t>0.0916538797298983</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>8.79</t>
+          <t>0.0878785218245616</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>8.54</t>
+          <t>0.0854357390211285</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>8.75</t>
+          <t>0.0874990840365595</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>0.0914384120263447</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>8.24</t>
+          <t>0.082438493593804</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>8.14</t>
+          <t>0.0813780100269325</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>8.14</t>
+          <t>0.0813764677007675</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>0.0771549705091588</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>7.48</t>
+          <t>0.0747580974960919</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>7.13</t>
+          <t>0.0713469850704996</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>0.317482200729191</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>30.91</t>
+          <t>0.309088660680667</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>30.39</t>
+          <t>0.30385045267517</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>29.91</t>
+          <t>0.299125413996663</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>0.287990073941307</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>28.06</t>
+          <t>0.280566266231395</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>27.69</t>
+          <t>0.276947622436025</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>0.269835123315949</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>28.93</t>
+          <t>0.289305228332656</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>25.27</t>
+          <t>0.252709126453133</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>24.76</t>
+          <t>0.24760798699191</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>0.243233587660924</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>24.36</t>
+          <t>0.24360542189321</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>23.88</t>
+          <t>0.23884218339719</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>23.02</t>
+          <t>0.230249244057891</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>31.12</t>
+          <t>0.311210423639795</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>30.28</t>
+          <t>0.302816883592597</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>29.76</t>
+          <t>0.297578675591064</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>29.29</t>
+          <t>0.292853636915592</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>28.17</t>
+          <t>0.281718296863938</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>27.43</t>
+          <t>0.274294489159972</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>27.07</t>
+          <t>0.270675845366228</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>26.36</t>
+          <t>0.263563346248278</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>28.3</t>
+          <t>0.283033451269207</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>24.64</t>
+          <t>0.246437349393838</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>24.13</t>
+          <t>0.241336209934075</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>23.7</t>
+          <t>0.236961810604399</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>23.73</t>
+          <t>0.237333644837161</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>23.26</t>
+          <t>0.232570406340265</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>0.223977466996279</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>compensation.empe_ls.r.pc</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>WIOD13</t>
